--- a/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt1_rubricas.xlsx
@@ -1968,13 +1968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1413F9-EFC4-46A0-81F4-C066756B337F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E521E49A-AC98-4A22-9E24-63B6509292B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99CB9889-87A8-4AA3-94B0-E300F69E4A37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1F6C241-7E1E-40BB-9BFE-A301DB39F6AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{072A5CBD-D208-4CAA-AB5C-7179C4DAF232}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ABF6B04-CD2E-4985-B1EB-CB4B43A71745}"/>
 </file>